--- a/ci-cd-merge-resolver/repoCollector/datasets/Chronicle-Queue.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/Chronicle-Queue.xlsx
@@ -150,7 +150,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -165,7 +165,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.0010000000474974513</v>
+        <v>0.15600000321865082</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>0</v>
@@ -182,7 +182,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>66.0</v>
+        <v>264.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>1.0</v>
@@ -197,7 +197,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.7449999451637268</v>
+        <v>5.540999889373779</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>0</v>
